--- a/runs/JET-20260824-028/output/JE-Recon-and-DIC-Template.xlsx
+++ b/runs/JET-20260824-028/output/JE-Recon-and-DIC-Template.xlsx
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Trial balance has duplicate account numbers</t>
+          <t>Trial balance has duplicate account numbers within the same fiscal period</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
